--- a/nriss-patch-2/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-procedure-imaging-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$103</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3752" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3717" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -805,27 +805,10 @@
     <t>A reference to a resource that contains details of the request for this procedure.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=(various e.g. PROC, OBS, PCPR, ACT,  moodCode=RQO].code</t>
-  </si>
-  <si>
-    <t>Procedure.basedOn:serviceRequestAccessionNumber</t>
-  </si>
-  <si>
-    <t>serviceRequestAccessionNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Référence à la demande d'examen contenant l'Accession Number</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -835,11 +818,11 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-administration-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-procedure-imaging-document|0.1.0)
 </t>
   </si>
   <si>
-    <t>Produits administrés pendant l'acte d'imagerie</t>
+    <t>Produits administrés pendant l'acte d'imagerie, ou procédures d'imagerie associées</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -956,7 +939,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260916095453</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1326,7 +1309,7 @@
     <t>Procedure.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-bio-chapter-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1999,12 +1982,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN104"/>
+  <dimension ref="A1:AN103"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.20703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.45703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.09765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.8984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6592,7 +6575,7 @@
         <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>77</v>
@@ -6646,14 +6629,16 @@
         <v>77</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>247</v>
@@ -6671,30 +6656,28 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
+      <c r="B42" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="D42" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6704,7 +6687,7 @@
         <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6713,15 +6696,17 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N42" s="2"/>
+      <c r="N42" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6770,7 +6755,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6785,10 +6770,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6799,42 +6784,42 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6860,13 +6845,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6884,13 +6869,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6899,56 +6884,56 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>270</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6974,34 +6959,34 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="AG44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>87</v>
@@ -7013,13 +6998,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>275</v>
+        <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7027,14 +7012,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7056,14 +7041,12 @@
         <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7088,31 +7071,31 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7127,38 +7110,38 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>77</v>
@@ -7170,13 +7153,17 @@
         <v>202</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7200,13 +7187,11 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7224,7 +7209,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7239,28 +7224,28 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7279,20 +7264,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7316,32 +7297,34 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>87</v>
@@ -7353,32 +7336,32 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
@@ -7393,15 +7376,17 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7450,10 +7435,10 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>87</v>
@@ -7465,24 +7450,24 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7505,16 +7490,16 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7564,7 +7549,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7579,24 +7564,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7619,17 +7604,15 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>323</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7678,7 +7661,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7693,19 +7676,19 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>330</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>331</v>
       </c>
@@ -7724,7 +7707,7 @@
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7733,13 +7716,13 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7808,10 +7791,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7819,10 +7802,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7833,10 +7816,10 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
@@ -7845,13 +7828,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7890,25 +7873,23 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
@@ -7917,13 +7898,13 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7931,10 +7912,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7945,25 +7926,25 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>344</v>
+        <v>153</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>345</v>
+        <v>154</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8002,35 +7983,37 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>155</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>348</v>
+        <v>156</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8041,21 +8024,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8067,15 +8050,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8124,19 +8109,19 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
@@ -8153,14 +8138,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8173,24 +8158,26 @@
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8238,7 +8225,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8256,7 +8243,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8274,38 +8261,36 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8330,13 +8315,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8354,39 +8339,39 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8394,7 +8379,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>87</v>
@@ -8409,17 +8394,17 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>202</v>
+        <v>363</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8444,34 +8429,34 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>87</v>
@@ -8483,24 +8468,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8508,7 +8493,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>87</v>
@@ -8520,20 +8505,20 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8582,10 +8567,10 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>87</v>
@@ -8597,26 +8582,28 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8625,30 +8612,28 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8696,13 +8681,13 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -8711,10 +8696,10 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>381</v>
+        <v>343</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8723,16 +8708,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8741,25 +8724,25 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>153</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>345</v>
+        <v>154</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8810,25 +8793,25 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>342</v>
+        <v>155</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>348</v>
+        <v>156</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8839,21 +8822,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8865,15 +8848,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8922,19 +8907,19 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
@@ -8951,14 +8936,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8971,24 +8956,26 @@
         <v>77</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9036,7 +9023,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9054,7 +9041,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9065,45 +9052,43 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9128,13 +9113,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9152,39 +9137,39 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9192,7 +9177,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>87</v>
@@ -9207,17 +9192,17 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9242,34 +9227,34 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AG64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>87</v>
@@ -9281,24 +9266,24 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9306,7 +9291,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>87</v>
@@ -9318,20 +9303,20 @@
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>209</v>
+        <v>372</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9380,10 +9365,10 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>87</v>
@@ -9395,26 +9380,28 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9423,30 +9410,28 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>377</v>
+        <v>338</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>379</v>
+        <v>340</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9494,13 +9479,13 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
@@ -9509,10 +9494,10 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>381</v>
+        <v>343</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9521,16 +9506,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9539,25 +9522,25 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>345</v>
+        <v>154</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9608,25 +9591,25 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>342</v>
+        <v>155</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>348</v>
+        <v>156</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9637,21 +9620,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9663,15 +9646,17 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9720,19 +9705,19 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
@@ -9749,14 +9734,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9769,24 +9754,26 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9834,7 +9821,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9852,7 +9839,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9863,45 +9850,43 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>353</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9926,13 +9911,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9950,39 +9935,39 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9990,7 +9975,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -10005,17 +9990,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10040,34 +10025,34 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AG71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>87</v>
@@ -10079,24 +10064,24 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10104,7 +10089,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>87</v>
@@ -10116,20 +10101,20 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10178,10 +10163,10 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>87</v>
@@ -10193,24 +10178,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10230,20 +10215,20 @@
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10292,7 +10277,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10310,10 +10295,10 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10321,10 +10306,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10335,7 +10320,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10347,18 +10332,18 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>402</v>
+        <v>202</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
         <v>405</v>
       </c>
+      <c r="N74" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -10382,13 +10367,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -10406,13 +10391,13 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
@@ -10421,13 +10406,13 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10435,10 +10420,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10461,16 +10446,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>202</v>
+        <v>413</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10496,31 +10481,31 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10535,24 +10520,24 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10566,7 +10551,7 @@
         <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10575,7 +10560,7 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>418</v>
+        <v>202</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>419</v>
@@ -10610,13 +10595,11 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>77</v>
+        <v>422</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10634,7 +10617,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10649,24 +10632,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>422</v>
+        <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10677,29 +10660,27 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>424</v>
+        <v>153</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10724,11 +10705,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -10746,50 +10729,50 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>423</v>
+        <v>155</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>428</v>
+        <v>156</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10801,15 +10784,17 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10846,31 +10831,31 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -10885,26 +10870,28 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>77</v>
@@ -10913,17 +10900,15 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>429</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>351</v>
+        <v>430</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10960,16 +10945,16 @@
         <v>77</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>160</v>
@@ -10990,7 +10975,7 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10999,16 +10984,14 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>432</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C80" t="s" s="2">
         <v>433</v>
       </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11020,7 +11003,7 @@
         <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>77</v>
@@ -11029,13 +11012,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>434</v>
+        <v>152</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>435</v>
+        <v>153</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>436</v>
+        <v>154</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11086,25 +11069,25 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11115,10 +11098,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11129,7 +11112,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11141,13 +11124,13 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11186,37 +11169,37 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11227,10 +11210,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11238,10 +11221,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -11253,22 +11236,24 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>77</v>
+        <v>438</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>77</v>
@@ -11298,37 +11283,37 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11339,10 +11324,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11365,24 +11350,22 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>77</v>
@@ -11424,10 +11407,10 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>87</v>
@@ -11436,7 +11419,7 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
@@ -11453,10 +11436,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11464,10 +11447,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -11476,19 +11459,23 @@
         <v>77</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>170</v>
+        <v>442</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>171</v>
+        <v>443</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
@@ -11536,13 +11523,13 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>173</v>
+        <v>447</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
@@ -11554,21 +11541,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>130</v>
+        <v>448</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11579,7 +11566,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -11591,19 +11578,19 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>447</v>
+        <v>152</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11652,13 +11639,13 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
@@ -11670,21 +11657,21 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11707,20 +11694,18 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -11744,13 +11729,13 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>77</v>
@@ -11768,7 +11753,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11786,21 +11771,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>462</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11811,7 +11796,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -11820,19 +11805,19 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>202</v>
+        <v>466</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11858,13 +11843,13 @@
         <v>77</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>467</v>
+        <v>77</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -11882,13 +11867,13 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>77</v>
@@ -11900,7 +11885,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11911,10 +11896,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11937,7 +11922,7 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>471</v>
+        <v>202</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>472</v>
@@ -11972,13 +11957,13 @@
         <v>77</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>77</v>
+        <v>475</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
@@ -11996,7 +11981,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12014,7 +11999,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12025,10 +12010,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12039,7 +12024,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>77</v>
@@ -12051,17 +12036,15 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>477</v>
+        <v>153</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>479</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12086,13 +12069,13 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>480</v>
+        <v>77</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -12110,25 +12093,25 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>476</v>
+        <v>155</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>482</v>
+        <v>156</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12139,21 +12122,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>77</v>
@@ -12165,15 +12148,17 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12210,31 +12195,31 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
@@ -12251,14 +12236,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12274,21 +12259,23 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>132</v>
+        <v>442</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>351</v>
+        <v>443</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>352</v>
+        <v>444</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -12324,19 +12311,19 @@
         <v>77</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>160</v>
+        <v>447</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12348,27 +12335,27 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>156</v>
+        <v>448</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12379,7 +12366,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
@@ -12391,19 +12378,19 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>447</v>
+        <v>152</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12452,13 +12439,13 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
@@ -12470,21 +12457,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12495,7 +12482,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
@@ -12504,22 +12491,20 @@
         <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>152</v>
+        <v>484</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12568,13 +12553,13 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>77</v>
@@ -12586,13 +12571,13 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>462</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" hidden="true">
@@ -12623,18 +12608,16 @@
         <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>492</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -12658,13 +12641,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>77</v>
+        <v>492</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -12700,7 +12683,7 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12711,10 +12694,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12737,13 +12720,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>202</v>
+        <v>495</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12770,13 +12753,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>497</v>
+        <v>77</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -12794,7 +12777,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12809,24 +12792,24 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>77</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12849,13 +12832,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>500</v>
+        <v>338</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12906,7 +12889,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12921,7 +12904,7 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>503</v>
+        <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>504</v>
@@ -12930,15 +12913,15 @@
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12949,7 +12932,7 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>77</v>
@@ -12961,13 +12944,13 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>507</v>
+        <v>153</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>508</v>
+        <v>154</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13018,25 +13001,25 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>506</v>
+        <v>155</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>509</v>
+        <v>156</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -13047,21 +13030,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>77</v>
@@ -13073,15 +13056,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13130,19 +13115,19 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
@@ -13159,14 +13144,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13179,24 +13164,26 @@
         <v>77</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="O99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
       </c>
@@ -13244,7 +13231,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>160</v>
+        <v>352</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13262,7 +13249,7 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -13273,46 +13260,42 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>355</v>
+        <v>509</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
       </c>
@@ -13336,13 +13319,13 @@
         <v>77</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>77</v>
+        <v>511</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>77</v>
+        <v>512</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>77</v>
@@ -13360,25 +13343,25 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>357</v>
+        <v>508</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>130</v>
+        <v>513</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -13389,10 +13372,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13400,7 +13383,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>87</v>
@@ -13415,13 +13398,13 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13448,13 +13431,13 @@
         <v>77</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>516</v>
+        <v>77</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>77</v>
@@ -13472,10 +13455,10 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>87</v>
@@ -13490,21 +13473,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AM101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="B102" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13512,13 +13495,13 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>77</v>
@@ -13527,16 +13510,20 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
@@ -13584,13 +13571,13 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>77</v>
@@ -13602,7 +13589,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13611,12 +13598,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13630,7 +13617,7 @@
         <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>77</v>
@@ -13639,20 +13626,18 @@
         <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>399</v>
+        <v>202</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
       </c>
@@ -13676,13 +13661,13 @@
         <v>77</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>77</v>
+        <v>527</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>77</v>
+        <v>528</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>77</v>
@@ -13700,7 +13685,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13718,131 +13703,17 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN104" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN104">
+  <autoFilter ref="A1:AN103">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13852,7 +13723,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI103">
+  <conditionalFormatting sqref="A2:AI102">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
